--- a/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="GL Balances" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AR by Customer" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AP by Supplier" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cash by Bank" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Fixed Assets" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Control Acct Recon" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GL Balances" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR by Customer" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AP by Supplier" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash by Bank" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Acct Recon" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,12 +66,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="6">
@@ -98,7 +103,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -147,21 +152,24 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -596,7 +604,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -706,18 +714,22 @@
           <t>Accounts Receivable (1100)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>3360000</v>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C16" s="7" t="n">
         <v>3360000</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>SKIP</t>
         </is>
       </c>
     </row>
@@ -727,18 +739,22 @@
           <t>Accounts Payable (2010)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>1368000</v>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C17" s="7" t="n">
         <v>1368000</v>
       </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>SKIP</t>
         </is>
       </c>
     </row>
@@ -749,17 +765,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>1438500</v>
+        <v>0</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>0</v>
+      <c r="D18" s="8" t="n">
+        <v>-1438500</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>MATCH</t>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -782,13 +798,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -871,239 +887,239 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>1020</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Cash at Bank — Main Account</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Cash in hand</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Current Asset</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>10100</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Cash at Bank</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>1500000</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>5440000</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>5501500</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I6" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>4.1%</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>1030</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Petty Cash</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>11000</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Current Asset</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Account Receivable</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G6" s="9" t="n">
+      <c r="F7" s="10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>4540000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1965000</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>2605000</v>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>8583.3%</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Inventory - Raw Material</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I9" s="7" t="n">
         <v>100000</v>
       </c>
-      <c r="H6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Current Asset</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>800000</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>4525000</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>1965000</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>3360000</v>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>320.0%</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>1110</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Allowance for Doubtful Debts</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Current Asset</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Inventory — Raw Materials</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Current Asset</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>450000</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>1320</v>
+        <v>15100</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Prepaid Insurance</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1113,7 +1129,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Current Asset</t>
+          <t>Property,Plant and Equipment</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1122,31 +1138,31 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>120000</v>
+        <v>5000000</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>100000</v>
+        <v>5000000</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>1610</v>
+        <v>15110</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Buildings</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1156,16 +1172,16 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Asset</t>
+          <t>Property,Plant and Equipment</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -1174,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -1185,11 +1201,11 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>1611</v>
+        <v>15200</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Buildings</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1199,16 +1215,16 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Asset</t>
+          <t>Property,Plant and Equipment</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -1217,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -1228,11 +1244,11 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>1620</v>
+        <v>15210</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Plant &amp; Machinery</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1242,16 +1258,16 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Asset</t>
+          <t>Property,Plant and Equipment</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>3000000</v>
+        <v>450000</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -1260,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>3000000</v>
+        <v>450000</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1271,11 +1287,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>1621</v>
+        <v>15300</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Plant &amp; Machinery</t>
+          <t>Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1285,16 +1301,16 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Asset</t>
+          <t>Property,Plant and Equipment</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>0</v>
@@ -1303,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -1314,11 +1330,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>1630</v>
+        <v>15310</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Furniture &amp; Fixtures</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1328,16 +1344,16 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Asset</t>
+          <t>Property,Plant and Equipment</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>0</v>
@@ -1346,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>800000</v>
+        <v>100000</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -1356,70 +1372,74 @@
       <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>1631</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Account 1631</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Non-Current Asset</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="A16" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Account Payables</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>160000</v>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>798000</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>1916000</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>447.2%</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>1650</v>
+        <v>21000</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Office Equipment</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Asset</t>
+          <t>Short-term loans</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
@@ -1443,21 +1463,21 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>1651</v>
+        <v>22200</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Office Equipment</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Asset</t>
+          <t>Accured Expenses</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1466,106 +1486,102 @@
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0</v>
+        <v>205000</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>100000</v>
+        <v>205000</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Current Liability</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>798000</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>1916000</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>1368000</v>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>447.2%</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
+      <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>2030</v>
+        <v>30200</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Accrued Wages &amp; Salaries</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Current Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>205000</v>
+        <v>0</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>205000</v>
+        <v>200000</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -1576,21 +1592,21 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>2060</v>
+        <v>31000</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Current Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1599,41 +1615,41 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
+        <v>7180000</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="n">
         <v>500000</v>
       </c>
-      <c r="G21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" s="7" t="n">
-        <v>500000</v>
+        <v>7680000</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>2100</v>
+        <v>32000</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Long-term Loans</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Non-Current Liability</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1642,7 +1658,7 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>2000000</v>
+        <v>1200000</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>0</v>
@@ -1651,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>2000000</v>
+        <v>1200000</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -1662,21 +1678,21 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>3010</v>
+        <v>40000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Owner's Capital</t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1685,41 +1701,41 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7180000</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>500000</v>
+        <v>7515000</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>7680000</v>
+        <v>7515000</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>3020</v>
+        <v>50000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Owner's Drawings</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1731,13 +1747,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>200000</v>
+        <v>2096000</v>
       </c>
       <c r="H24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>200000</v>
+        <v>2096000</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -1748,82 +1764,82 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>3030</v>
+        <v>50100</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>1200000</v>
+        <v>225000</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>4010</v>
+        <v>60000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 1</t>
+          <t>Marketing &amp; Advertising Expense</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>1710000</v>
+        <v>0</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1710000</v>
+        <v>120000</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -1834,39 +1850,39 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>4020</v>
+        <v>61000</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 2</t>
+          <t>Office Salaries</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0</v>
+        <v>2755000</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>2090000</v>
+        <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>2090000</v>
+        <v>2755000</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1877,39 +1893,39 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>4030</v>
+        <v>62000</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — Shop 3</t>
+          <t>Meal Allowance Expense</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>1310000</v>
+        <v>0</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>1310000</v>
+        <v>120000</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -1920,39 +1936,39 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>4040</v>
+        <v>63000</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue — General</t>
+          <t>Utilities (Electricity &amp; Water)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Operating Revenue</t>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>2405000</v>
+        <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>2405000</v>
+        <v>125000</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -1963,11 +1979,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>5010</v>
+        <v>64000</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Raw Materials Used</t>
+          <t>Transportation &amp; Distribution Expense</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1977,7 +1993,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1989,13 +2005,13 @@
         <v>0</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>2096000</v>
+        <v>85000</v>
       </c>
       <c r="H30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>2096000</v>
+        <v>85000</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -2006,11 +2022,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>5020</v>
+        <v>65000</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Packaging Costs</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2020,7 +2036,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -2032,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>225000</v>
+        <v>1468500</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>225000</v>
+        <v>1468500</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -2049,11 +2065,11 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>5100</v>
+        <v>67000</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Salaries &amp; Wages</t>
+          <t>Inventory Write-off</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2063,7 +2079,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Operating Expense</t>
+          <t>SG&amp;A</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -2075,13 +2091,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>2755000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>2755000</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -2090,517 +2106,44 @@
       </c>
       <c r="K32" s="6" t="inlineStr"/>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="n">
-        <v>5110</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Employee Benefits</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr"/>
-    </row>
+    <row r="33"/>
     <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>5200</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Rent Expense</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>1180000</v>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr"/>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Total Debit Balances</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n">
+        <v>20138000</v>
+      </c>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>5210</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Utilities Expense</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
-        <v>5220</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>55000</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>55000</v>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>5400</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Repairs &amp; Maintenance</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>95000</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>95000</v>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
-        <v>5420</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Cleaning &amp; Sanitation</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Delivery</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
-        <v>5600</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Advertising</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>5700</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Expense</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>5800</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Bad Debt Expense</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>5920</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Bank Charges &amp; Fees</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Non-Operating Expense</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>8500</v>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Total Debit Balances</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="11" t="n">
-        <v>21693000</v>
-      </c>
-      <c r="J45" s="11" t="n"/>
-      <c r="K45" s="11" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Total Credit Balances</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
-      <c r="I46" s="11" t="n">
-        <v>21693000</v>
-      </c>
-      <c r="J46" s="11" t="n"/>
-      <c r="K46" s="11" t="n"/>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n">
+        <v>21518000</v>
+      </c>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2941,15 +2484,15 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n">
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n">
         <v>3360000</v>
       </c>
     </row>
@@ -3121,15 +2664,15 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n">
         <v>1368000</v>
       </c>
     </row>
@@ -3225,15 +2768,15 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n">
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n">
         <v>1438500</v>
       </c>
     </row>
@@ -3334,7 +2877,7 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1610</v>
+        <v>15100</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -3373,7 +2916,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1610</v>
+        <v>15100</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -3412,7 +2955,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1620</v>
+        <v>15200</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
@@ -3451,7 +2994,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1620</v>
+        <v>15200</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -3490,7 +3033,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1630</v>
+        <v>15300</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
@@ -3529,7 +3072,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>1630</v>
+        <v>15300</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
@@ -3568,7 +3111,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>1650</v>
+        <v>15300</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -3607,7 +3150,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>1650</v>
+        <v>15300</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
@@ -3636,25 +3179,25 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n">
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n">
         <v>9300000</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="14" t="n">
         <v>1404500</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>7895500</v>
       </c>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3726,17 +3269,17 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>3360000</v>
+        <v>0</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>3360000</v>
       </c>
-      <c r="D4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="D4" s="8" t="n">
+        <v>-3360000</v>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3747,17 +3290,17 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1368000</v>
+        <v>0</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1368000</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="D5" s="8" t="n">
+        <v>-1368000</v>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3768,17 +3311,17 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1438500</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+      <c r="D6" s="8" t="n">
+        <v>-1438500</v>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>

--- a/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1072,11 +1072,11 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>13000</v>
+        <v>12200</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Advanced Payments</t>
+          <t>Inventory - Finished Goods</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Advanced Payments</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1095,31 +1095,31 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>100000</v>
+        <v>260000</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>15100</v>
+        <v>12400</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Buildings &amp; Structures</t>
+          <t>Work-in-Progress</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Property,Plant and Equipment</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>5000000</v>
+        <v>50000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>5000000</v>
+        <v>65000</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>15110</v>
+        <v>13000</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1172,40 +1172,40 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Property,Plant and Equipment</t>
+          <t>Advanced Payments</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>500000</v>
+        <v>120000</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Machinery &amp; Equipment</t>
+          <t>Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -1244,11 +1244,11 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>15210</v>
+        <v>15110</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -1287,11 +1287,11 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>15300</v>
+        <v>15200</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Office &amp; Facility Equipment</t>
+          <t>Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -1330,11 +1330,11 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>15310</v>
+        <v>15210</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>100000</v>
+        <v>450000</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>100000</v>
+        <v>450000</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -1372,145 +1372,145 @@
       <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Account Payables</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>798000</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>1916000</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>1368000</v>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>447.2%</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
+      <c r="A16" s="6" t="n">
+        <v>15300</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>21000</v>
+        <v>15310</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Short-term Loans</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
           <t>Liability</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Short-term loans</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Account Payables</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>22200</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Wages Payable</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Accured Expenses</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>205000</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>205000</v>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr"/>
+      <c r="F18" s="10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>798000</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>1916000</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>447.2%</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>25000</v>
+        <v>21000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Short-term Loans</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>Short-term loans</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -1549,39 +1549,39 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>30200</v>
+        <v>22200</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Account 30200</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Accured Expenses</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0</v>
+        <v>205000</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>200000</v>
+        <v>205000</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Paid-up Capital</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Liability</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1615,31 +1615,31 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>7180000</v>
+        <v>2000000</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>7680000</v>
+        <v>2000000</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>32000</v>
+        <v>30200</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Account 30200</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1649,50 +1649,50 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1200000</v>
+        <v>200000</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>40000</v>
+        <v>31000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Sales Revenue</t>
+          <t>Paid-up Capital</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1701,102 +1701,102 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0</v>
+        <v>7180000</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>7515000</v>
+        <v>500000</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>7515000</v>
+        <v>7680000</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>50000</v>
+        <v>32000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Cost of Production</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>2096000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>2096000</v>
+        <v>1200000</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>50100</v>
+        <v>40000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Cost of Production</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>225000</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0</v>
+        <v>7515000</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>225000</v>
+        <v>7515000</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -1807,11 +1807,11 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Marketing &amp; Advertising Expense</t>
+          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1833,13 +1833,13 @@
         <v>0</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>120000</v>
+        <v>2096000</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>120000</v>
+        <v>2096000</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -1850,11 +1850,11 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>61000</v>
+        <v>50100</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Office Salaries</t>
+          <t xml:space="preserve">Opening Inventory - Packaging </t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1876,13 +1876,13 @@
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>2755000</v>
+        <v>225000</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -1893,11 +1893,11 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>62000</v>
+        <v>50300</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Meal Allowance Expense</t>
+          <t>Opening Work-in-Progress</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1916,31 +1916,31 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>63000</v>
+        <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Utilities (Electricity &amp; Water)</t>
+          <t>Closing Work-in-Progress</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1962,13 +1962,13 @@
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>125000</v>
+        <v>65000</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>-65000</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -1979,11 +1979,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>64000</v>
+        <v>50320</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Transportation &amp; Distribution Expense</t>
+          <t>Direct Materials Used</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -2005,13 +2005,13 @@
         <v>0</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>85000</v>
+        <v>150000</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -2022,11 +2022,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>65000</v>
+        <v>50330</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+          <t>Direct Labor Transferred to WIP</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>SG&amp;A</t>
+          <t>Cost of Production</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -2048,13 +2048,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>1468500</v>
+        <v>80000</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1468500</v>
+        <v>0</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -2065,85 +2065,429 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
+        <v>50340</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Manufacturing Overhead Applied</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Cost of Production</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>50350</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>WIP Transferred to Finished Goods</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Cost of Production</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>260000</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>260000</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Advertising Expense</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>61000</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Office Salaries</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>62000</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Meal Allowance Expense</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>63000</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Utilities (Electricity &amp; Water)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>64000</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>1468500</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>1468500</v>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
         <v>67000</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Inventory Write-off</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>SG&amp;A</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Total Debit Balances</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n">
-        <v>20138000</v>
-      </c>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n">
+        <v>20448000</v>
+      </c>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Total Credit Balances</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n">
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n">
         <v>21518000</v>
       </c>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +78,12 @@
       <b val="1"/>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +108,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -170,6 +179,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -711,71 +723,63 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Accounts Receivable (1100)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Accounts Receivable (11000)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>2605000</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>3360000</v>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D16" s="8" t="n">
+        <v>-755000</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Accounts Payable (2010)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Accounts Payable (20000)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>1368000</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>1368000</v>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank (1020)</t>
+          <t>Cash at Bank (10100)</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0</v>
+        <v>1438500</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>-1438500</v>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>MISMATCH</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3613,17 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>AR — Accts Receivable (1100)</t>
+          <t>AR — Accts Receivable (11000)</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0</v>
+        <v>2605000</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>3360000</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>-3360000</v>
+        <v>-755000</v>
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
@@ -3630,42 +3634,42 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>AP — Accts Payable (2010)</t>
+          <t>AP — Accts Payable (20000)</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0</v>
+        <v>1368000</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1368000</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>-1368000</v>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="D5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank (1020–1022)</t>
+          <t>Cash at Bank (10100)</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>0</v>
+        <v>1438500</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>-1438500</v>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="D6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
     </row>

--- a/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/ledger_summary_Jan2026.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -684,100 +684,130 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Raw Materials Ledger</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Packaging Ledger</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CONTROL ACCOUNT RECONCILIATION</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>GL Balance</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Subsidiary Total</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Accounts Receivable (11000)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>2605000</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>3360000</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>-755000</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Accounts Payable (20000)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>1368000</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>1368000</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>Accounts Receivable (11000)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>2605000</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>-755000</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Accounts Payable (20000)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>Cash at Bank (10100)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B20" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C20" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -785,11 +815,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
